--- a/Team-Data/2013-14/11-21-2013-14.xlsx
+++ b/Team-Data/2013-14/11-21-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,13 +806,13 @@
         <v>3</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
@@ -757,10 +824,10 @@
         <v>11</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL2" t="n">
         <v>11</v>
@@ -790,7 +857,7 @@
         <v>26</v>
       </c>
       <c r="AU2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -924,7 +991,7 @@
         <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF3" t="n">
         <v>29</v>
@@ -951,7 +1018,7 @@
         <v>26</v>
       </c>
       <c r="AN3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO3" t="n">
         <v>24</v>
@@ -987,13 +1054,13 @@
         <v>16</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
         <v>24</v>
       </c>
       <c r="BB3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC3" t="n">
         <v>26</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1188,7 @@
         <v>25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
         <v>21</v>
@@ -1139,7 +1206,7 @@
         <v>4</v>
       </c>
       <c r="AP4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ4" t="n">
         <v>15</v>
@@ -1163,7 +1230,7 @@
         <v>21</v>
       </c>
       <c r="AX4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY4" t="n">
         <v>5</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-3.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
         <v>13</v>
@@ -1303,7 +1370,7 @@
         <v>30</v>
       </c>
       <c r="AJ5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1318,13 +1385,13 @@
         <v>28</v>
       </c>
       <c r="AO5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AP5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR5" t="n">
         <v>11</v>
@@ -1342,7 +1409,7 @@
         <v>3</v>
       </c>
       <c r="AW5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -1389,133 +1456,133 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="J6" t="n">
-        <v>81.2</v>
+        <v>79.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.427</v>
+        <v>0.433</v>
       </c>
       <c r="L6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="M6" t="n">
-        <v>15.2</v>
+        <v>15.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0.342</v>
+        <v>0.345</v>
       </c>
       <c r="O6" t="n">
-        <v>18.7</v>
+        <v>19.9</v>
       </c>
       <c r="P6" t="n">
-        <v>22.7</v>
+        <v>23.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.824</v>
+        <v>0.84</v>
       </c>
       <c r="R6" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="S6" t="n">
-        <v>34.3</v>
+        <v>34.1</v>
       </c>
       <c r="T6" t="n">
-        <v>47.1</v>
+        <v>45.9</v>
       </c>
       <c r="U6" t="n">
         <v>22.1</v>
       </c>
       <c r="V6" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="W6" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="X6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>21</v>
+        <v>21.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.3</v>
+        <v>94</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AD6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
       </c>
       <c r="AF6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG6" t="n">
         <v>6</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10</v>
       </c>
       <c r="AH6" t="n">
         <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AK6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM6" t="n">
         <v>28</v>
       </c>
       <c r="AN6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AP6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
       </c>
       <c r="AR6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
         <v>6</v>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU6" t="n">
         <v>14</v>
@@ -1524,25 +1591,25 @@
         <v>24</v>
       </c>
       <c r="AW6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ6" t="n">
         <v>10</v>
       </c>
       <c r="BA6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BC6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>-7</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF7" t="n">
         <v>24</v>
@@ -1664,7 +1731,7 @@
         <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ7" t="n">
         <v>9</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -1831,13 +1898,13 @@
         <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG8" t="n">
         <v>6</v>
@@ -1852,25 +1919,25 @@
         <v>14</v>
       </c>
       <c r="AK8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL8" t="n">
         <v>4</v>
       </c>
       <c r="AM8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN8" t="n">
         <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR8" t="n">
         <v>23</v>
@@ -1894,7 +1961,7 @@
         <v>17</v>
       </c>
       <c r="AY8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ8" t="n">
         <v>16</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -1935,94 +2002,94 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.455</v>
+        <v>0.4</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="J9" t="n">
-        <v>88.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L9" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M9" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.378</v>
+        <v>0.373</v>
       </c>
       <c r="O9" t="n">
-        <v>18</v>
+        <v>18.6</v>
       </c>
       <c r="P9" t="n">
-        <v>25.8</v>
+        <v>26.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.697</v>
+        <v>0.71</v>
       </c>
       <c r="R9" t="n">
         <v>13.3</v>
       </c>
       <c r="S9" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="T9" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="U9" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V9" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y9" t="n">
         <v>6.5</v>
       </c>
-      <c r="X9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>6.2</v>
-      </c>
       <c r="Z9" t="n">
-        <v>22.2</v>
+        <v>22.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>23.4</v>
+        <v>23.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.7</v>
+        <v>104.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.2</v>
+        <v>-1.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AE9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AF9" t="n">
         <v>13</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AH9" t="n">
         <v>17</v>
@@ -2043,16 +2110,16 @@
         <v>18</v>
       </c>
       <c r="AN9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AP9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AR9" t="n">
         <v>3</v>
@@ -2061,7 +2128,7 @@
         <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="n">
         <v>15</v>
@@ -2070,25 +2137,25 @@
         <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA9" t="n">
         <v>4</v>
       </c>
       <c r="BB9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BC9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2265,7 @@
         <v>17</v>
       </c>
       <c r="AE10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF10" t="n">
         <v>18</v>
@@ -2207,7 +2274,7 @@
         <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI10" t="n">
         <v>12</v>
@@ -2231,7 +2298,7 @@
         <v>18</v>
       </c>
       <c r="AP10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ10" t="n">
         <v>30</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -2377,13 +2444,13 @@
         <v>6.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
         <v>5</v>
       </c>
       <c r="AF11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG11" t="n">
         <v>6</v>
@@ -2395,7 +2462,7 @@
         <v>9</v>
       </c>
       <c r="AJ11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK11" t="n">
         <v>3</v>
@@ -2416,13 +2483,13 @@
         <v>27</v>
       </c>
       <c r="AQ11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR11" t="n">
         <v>27</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT11" t="n">
         <v>13</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -2565,10 +2632,10 @@
         <v>5</v>
       </c>
       <c r="AF12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AH12" t="n">
         <v>4</v>
@@ -2598,7 +2665,7 @@
         <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR12" t="n">
         <v>19</v>
@@ -2607,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="AT12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU12" t="n">
         <v>16</v>
@@ -2625,7 +2692,7 @@
         <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2634,7 +2701,7 @@
         <v>1</v>
       </c>
       <c r="BC12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2820,7 @@
         <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
@@ -2774,7 +2841,7 @@
         <v>14</v>
       </c>
       <c r="AO13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP13" t="n">
         <v>11</v>
@@ -2786,7 +2853,7 @@
         <v>26</v>
       </c>
       <c r="AS13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
         <v>10</v>
@@ -2795,7 +2862,7 @@
         <v>19</v>
       </c>
       <c r="AV13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -2845,94 +2912,94 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
         <v>8</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>0.615</v>
+        <v>0.667</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="J14" t="n">
-        <v>83.8</v>
+        <v>83.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0.473</v>
+        <v>0.479</v>
       </c>
       <c r="L14" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="M14" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.347</v>
+        <v>0.353</v>
       </c>
       <c r="O14" t="n">
-        <v>19.4</v>
+        <v>20.4</v>
       </c>
       <c r="P14" t="n">
-        <v>27.3</v>
+        <v>28.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.71</v>
+        <v>0.721</v>
       </c>
       <c r="R14" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S14" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T14" t="n">
-        <v>43.7</v>
+        <v>43.9</v>
       </c>
       <c r="U14" t="n">
         <v>25.7</v>
       </c>
       <c r="V14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="W14" t="n">
         <v>9.1</v>
       </c>
       <c r="X14" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.6</v>
+        <v>24.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.3</v>
+        <v>108.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
       </c>
       <c r="AF14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH14" t="n">
         <v>17</v>
@@ -2941,52 +3008,52 @@
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>9</v>
       </c>
       <c r="AM14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN14" t="n">
         <v>16</v>
       </c>
       <c r="AO14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR14" t="n">
         <v>8</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>10</v>
       </c>
       <c r="AS14" t="n">
         <v>15</v>
       </c>
       <c r="AT14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AW14" t="n">
         <v>8</v>
       </c>
       <c r="AX14" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AY14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ14" t="n">
         <v>29</v>
@@ -2998,7 +3065,7 @@
         <v>2</v>
       </c>
       <c r="BC14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-4.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>15</v>
@@ -3114,7 +3181,7 @@
         <v>18</v>
       </c>
       <c r="AG15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH15" t="n">
         <v>17</v>
@@ -3126,7 +3193,7 @@
         <v>4</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
         <v>2</v>
@@ -3144,7 +3211,7 @@
         <v>24</v>
       </c>
       <c r="AQ15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR15" t="n">
         <v>18</v>
@@ -3159,7 +3226,7 @@
         <v>6</v>
       </c>
       <c r="AV15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
         <v>28</v>
@@ -3171,7 +3238,7 @@
         <v>13</v>
       </c>
       <c r="AZ15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA15" t="n">
         <v>30</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -3287,13 +3354,13 @@
         <v>-1.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
@@ -3305,7 +3372,7 @@
         <v>18</v>
       </c>
       <c r="AJ16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK16" t="n">
         <v>8</v>
@@ -3317,7 +3384,7 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO16" t="n">
         <v>19</v>
@@ -3344,7 +3411,7 @@
         <v>8</v>
       </c>
       <c r="AW16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX16" t="n">
         <v>28</v>
@@ -3362,7 +3429,7 @@
         <v>23</v>
       </c>
       <c r="BC16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>9.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
@@ -3484,7 +3551,7 @@
         <v>17</v>
       </c>
       <c r="AI17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3502,10 +3569,10 @@
         <v>1</v>
       </c>
       <c r="AO17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
         <v>16</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3669,7 +3736,7 @@
         <v>29</v>
       </c>
       <c r="AJ18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK18" t="n">
         <v>27</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3903,7 @@
         <v>1</v>
       </c>
       <c r="AE19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF19" t="n">
         <v>13</v>
@@ -3875,7 +3942,7 @@
         <v>4</v>
       </c>
       <c r="AR19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS19" t="n">
         <v>10</v>
@@ -3896,7 +3963,7 @@
         <v>29</v>
       </c>
       <c r="AY19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4115,7 @@
         <v>3</v>
       </c>
       <c r="AO20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP20" t="n">
         <v>12</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4276,7 @@
         <v>27</v>
       </c>
       <c r="AH21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
@@ -4227,7 +4294,7 @@
         <v>2</v>
       </c>
       <c r="AN21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4257,7 +4324,7 @@
         <v>11</v>
       </c>
       <c r="AX21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY21" t="n">
         <v>12</v>
@@ -4269,7 +4336,7 @@
         <v>28</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC21" t="n">
         <v>25</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -4301,88 +4368,88 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>0.727</v>
+        <v>0.7</v>
       </c>
       <c r="H22" t="n">
         <v>48.5</v>
       </c>
       <c r="I22" t="n">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="J22" t="n">
-        <v>82.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.448</v>
+        <v>0.441</v>
       </c>
       <c r="L22" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="M22" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N22" t="n">
-        <v>0.315</v>
+        <v>0.325</v>
       </c>
       <c r="O22" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="P22" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.822</v>
       </c>
       <c r="R22" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="S22" t="n">
-        <v>34.5</v>
+        <v>34</v>
       </c>
       <c r="T22" t="n">
-        <v>47.1</v>
+        <v>46.9</v>
       </c>
       <c r="U22" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="V22" t="n">
         <v>16.8</v>
       </c>
       <c r="W22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.3</v>
+        <v>104.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AE22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AF22" t="n">
         <v>4</v>
@@ -4394,7 +4461,7 @@
         <v>8</v>
       </c>
       <c r="AI22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ22" t="n">
         <v>16</v>
@@ -4409,7 +4476,7 @@
         <v>20</v>
       </c>
       <c r="AN22" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AO22" t="n">
         <v>2</v>
@@ -4418,43 +4485,43 @@
         <v>2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AT22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB22" t="n">
         <v>7</v>
       </c>
-      <c r="AY22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>6</v>
-      </c>
       <c r="BC22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4631,7 @@
         <v>17</v>
       </c>
       <c r="AE23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF23" t="n">
         <v>18</v>
@@ -4573,7 +4640,7 @@
         <v>21</v>
       </c>
       <c r="AH23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI23" t="n">
         <v>14</v>
@@ -4609,7 +4676,7 @@
         <v>11</v>
       </c>
       <c r="AT23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU23" t="n">
         <v>17</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -4782,13 +4849,13 @@
         <v>14</v>
       </c>
       <c r="AQ24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR24" t="n">
         <v>15</v>
       </c>
       <c r="AS24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT24" t="n">
         <v>7</v>
@@ -4806,7 +4873,7 @@
         <v>19</v>
       </c>
       <c r="AY24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ24" t="n">
         <v>5</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -4937,7 +5004,7 @@
         <v>15</v>
       </c>
       <c r="AH25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI25" t="n">
         <v>16</v>
@@ -4952,7 +5019,7 @@
         <v>7</v>
       </c>
       <c r="AM25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN25" t="n">
         <v>12</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>5.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -5149,7 +5216,7 @@
         <v>13</v>
       </c>
       <c r="AR26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS26" t="n">
         <v>13</v>
@@ -5167,7 +5234,7 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY26" t="n">
         <v>1</v>
@@ -5179,7 +5246,7 @@
         <v>18</v>
       </c>
       <c r="BB26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5359,7 @@
         <v>17</v>
       </c>
       <c r="AE27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF27" t="n">
         <v>18</v>
@@ -5307,7 +5374,7 @@
         <v>22</v>
       </c>
       <c r="AJ27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK27" t="n">
         <v>24</v>
@@ -5322,10 +5389,10 @@
         <v>23</v>
       </c>
       <c r="AO27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ27" t="n">
         <v>6</v>
@@ -5346,7 +5413,7 @@
         <v>1</v>
       </c>
       <c r="AW27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX27" t="n">
         <v>30</v>
@@ -5358,7 +5425,7 @@
         <v>24</v>
       </c>
       <c r="BA27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB27" t="n">
         <v>22</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5559,7 @@
         <v>14</v>
       </c>
       <c r="AK28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL28" t="n">
         <v>16</v>
@@ -5501,7 +5568,7 @@
         <v>22</v>
       </c>
       <c r="AN28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5534,7 +5601,7 @@
         <v>26</v>
       </c>
       <c r="AY28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>0.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
         <v>15</v>
@@ -5662,7 +5729,7 @@
         <v>18</v>
       </c>
       <c r="AG29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH29" t="n">
         <v>2</v>
@@ -5683,10 +5750,10 @@
         <v>15</v>
       </c>
       <c r="AN29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP29" t="n">
         <v>7</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -5853,13 +5920,13 @@
         <v>28</v>
       </c>
       <c r="AJ30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK30" t="n">
         <v>28</v>
       </c>
       <c r="AL30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM30" t="n">
         <v>24</v>
@@ -5874,10 +5941,10 @@
         <v>13</v>
       </c>
       <c r="AQ30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS30" t="n">
         <v>27</v>
@@ -5901,10 +5968,10 @@
         <v>18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB30" t="n">
         <v>29</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6087,7 @@
         <v>17</v>
       </c>
       <c r="AE31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF31" t="n">
         <v>18</v>
@@ -6071,7 +6138,7 @@
         <v>4</v>
       </c>
       <c r="AV31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW31" t="n">
         <v>5</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-21-2013-14</t>
+          <t>2013-11-21</t>
         </is>
       </c>
     </row>
